--- a/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blin.berdoniqi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{4DE356E2-5E12-4618-9FFB-C2B3968440F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62BAB883-B009-4E0C-82F4-1C771BE02629}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{4DE356E2-5E12-4618-9FFB-C2B3968440F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86EDD422-57B0-45E4-A174-0EE571381309}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="95">
   <si>
     <t>Project ID</t>
   </si>
@@ -125,9 +128,6 @@
     <t>Renewable Energy</t>
   </si>
   <si>
-    <t>00124575</t>
-  </si>
-  <si>
     <t>Transport Services</t>
   </si>
   <si>
@@ -146,16 +146,10 @@
     <t>Energy Efficiency</t>
   </si>
   <si>
-    <t>00124576</t>
-  </si>
-  <si>
     <t>3 systems installed 125.93 MWh/year) MW</t>
   </si>
   <si>
     <t xml:space="preserve">In 2023, three solar photovoltaic (PV) systems will be installed in public buildings, benefiting the municipalities of Prizren and Suhareka. </t>
-  </si>
-  <si>
-    <t>00124577</t>
   </si>
   <si>
     <t>Campaign Participant</t>
@@ -205,40 +199,49 @@
     <t>Member of Climate Change Council trained for NDC development</t>
   </si>
   <si>
+    <t>Education Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A training program for solar installers has attracted individuals interested in energy activities. The program aimed to equip participants with the necessary skills for solar system installation. Out of the 35 individuals who enrolled in the training, 28 individuals successfully completed the program and earned their certification in solar system installation. </t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t># of companies trained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The green business accelerator, Boost x Kosovo, has successfully trained over 130 individuals and 50 companies in various aspects of sustainable practices. This program aims to accelerate the growth of green businesses and promote environmentally friendly initiatives. As a result, 32 participants were awarded grants totaling 332,000 euros. These grants will be utilized to support and enhance green transformation projects, such as the implementation of solar systems, biomass utilization, energy efficiency improvements, and more. </t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t># of individuals trained</t>
+  </si>
+  <si>
+    <t>The Earth Day campaigns and Energy Efficiency Campaigns successfully reached out to a wide audience, engaging at least 1600 individuals. These initiatives aimed to raise awareness about environmental conservation and the importance of energy efficiency.</t>
+  </si>
+  <si>
+    <t>00124575</t>
+  </si>
+  <si>
+    <t>00124576</t>
+  </si>
+  <si>
+    <t>00124577</t>
+  </si>
+  <si>
     <t>00130767</t>
   </si>
   <si>
-    <t>Education Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A training program for solar installers has attracted individuals interested in energy activities. The program aimed to equip participants with the necessary skills for solar system installation. Out of the 35 individuals who enrolled in the training, 28 individuals successfully completed the program and earned their certification in solar system installation. </t>
-  </si>
-  <si>
     <t>00130768</t>
   </si>
   <si>
     <t>https://boostimpact.org/challenges/the-kosovo-green-challenge/</t>
   </si>
   <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t># of companies trained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The green business accelerator, Boost x Kosovo, has successfully trained over 130 individuals and 50 companies in various aspects of sustainable practices. This program aims to accelerate the growth of green businesses and promote environmentally friendly initiatives. As a result, 32 participants were awarded grants totaling 332,000 euros. These grants will be utilized to support and enhance green transformation projects, such as the implementation of solar systems, biomass utilization, energy efficiency improvements, and more. </t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t># of individuals trained</t>
-  </si>
-  <si>
     <t>00130769</t>
-  </si>
-  <si>
-    <t>The Earth Day campaigns and Energy Efficiency Campaigns successfully reached out to a wide audience, engaging at least 1600 individuals. These initiatives aimed to raise awareness about environmental conservation and the importance of energy efficiency.</t>
   </si>
   <si>
     <t># of systems installed (53.76 KWp/70 MWh/year)</t>
@@ -591,7 +594,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -657,66 +660,6 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -741,6 +684,81 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1090,7 +1108,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="29" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="19" t="s">
@@ -1134,8 +1152,8 @@
       <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="25">
-        <v>1150000</v>
+      <c r="D2" s="36">
+        <v>1220000</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>22</v>
@@ -1149,44 +1167,38 @@
       <c r="H2" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="47" t="s">
+      <c r="K2" s="26"/>
+      <c r="L2" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="48"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45" t="s">
+      <c r="M2" s="28"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="45" t="s">
+      <c r="P2" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
     </row>
     <row r="3" spans="1:19" ht="167.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
@@ -1194,46 +1206,40 @@
       <c r="H3" s="6">
         <v>2</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="25"/>
+      <c r="L3" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="48" t="s">
+      <c r="N3" s="25"/>
+      <c r="O3" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45" t="s">
+      <c r="P3" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
     </row>
     <row r="4" spans="1:19" ht="60.75">
-      <c r="A4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="26"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -1241,44 +1247,38 @@
       <c r="H4" s="6">
         <v>0.04</v>
       </c>
-      <c r="I4" s="50" t="s">
+      <c r="I4" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+    </row>
+    <row r="5" spans="1:19" ht="76.5">
+      <c r="A5" s="14"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="J4" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="45"/>
-      <c r="L4" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="45"/>
-    </row>
-    <row r="5" spans="1:19" ht="76.5">
-      <c r="A5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -1286,42 +1286,42 @@
       <c r="H5" s="6">
         <v>100</v>
       </c>
-      <c r="I5" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="45" t="s">
+      <c r="I5" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="45"/>
-      <c r="L5" s="47" t="s">
+      <c r="K5" s="25"/>
+      <c r="L5" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
     </row>
     <row r="6" spans="1:19" ht="45.75">
       <c r="A6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="36">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="28">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -1329,38 +1329,32 @@
       <c r="H6" s="8">
         <v>15</v>
       </c>
-      <c r="I6" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
+      <c r="I6" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
     </row>
     <row r="7" spans="1:19" ht="137.25">
-      <c r="A7" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="15"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
@@ -1368,36 +1362,30 @@
       <c r="H7" s="8">
         <v>28</v>
       </c>
-      <c r="I7" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
+      <c r="I7" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
     </row>
     <row r="8" spans="1:19" ht="213">
-      <c r="A8" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="29"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="37"/>
       <c r="E8" s="22" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G8" s="24">
         <v>0</v>
@@ -1405,63 +1393,57 @@
       <c r="H8" s="23">
         <v>50</v>
       </c>
-      <c r="I8" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
+      <c r="I8" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="29"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="8">
         <v>130</v>
       </c>
-      <c r="I9" s="52"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
     </row>
     <row r="10" spans="1:19" ht="106.5">
-      <c r="A10" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="30"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="38"/>
       <c r="E10" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G10" s="8">
         <v>0</v>
@@ -1469,27 +1451,25 @@
       <c r="H10" s="8">
         <v>1600</v>
       </c>
-      <c r="I10" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
+      <c r="I10" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="D6:D10"/>
+  <mergeCells count="3">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
@@ -1615,7 +1595,7 @@
       <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="43">
         <v>1150000</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1650,7 +1630,7 @@
     </row>
     <row r="3" spans="1:19" ht="167.25">
       <c r="A3" s="14" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>20</v>
@@ -1658,12 +1638,12 @@
       <c r="C3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="26"/>
+      <c r="D3" s="44"/>
       <c r="E3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
@@ -1672,7 +1652,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
@@ -1681,18 +1661,18 @@
         <v>26</v>
       </c>
       <c r="M3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>34</v>
-      </c>
-      <c r="P3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="60.75">
       <c r="A4" s="14" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>20</v>
@@ -1700,12 +1680,12 @@
       <c r="C4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="26"/>
+      <c r="D4" s="44"/>
       <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -1714,7 +1694,7 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
@@ -1731,7 +1711,7 @@
     </row>
     <row r="5" spans="1:19" ht="76.5">
       <c r="A5" s="14" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>20</v>
@@ -1739,12 +1719,12 @@
       <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="45"/>
       <c r="E5" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -1753,7 +1733,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
         <v>25</v>
@@ -1764,22 +1744,22 @@
     </row>
     <row r="6" spans="1:19" ht="45.75">
       <c r="A6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="46">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="28">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -1788,28 +1768,28 @@
         <v>15</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="137.25">
       <c r="A7" s="15" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="47"/>
+      <c r="E7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
@@ -1818,25 +1798,25 @@
         <v>28</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="213">
-      <c r="A8" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="29"/>
+      <c r="A8" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="47"/>
       <c r="E8" s="22" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G8" s="24">
         <v>0</v>
@@ -1845,19 +1825,19 @@
         <v>50</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="29"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="47"/>
       <c r="E9" s="13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="8">
@@ -1867,20 +1847,20 @@
     </row>
     <row r="10" spans="1:19" ht="106.5">
       <c r="A10" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="30"/>
+        <v>42</v>
+      </c>
+      <c r="D10" s="48"/>
       <c r="E10" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G10" s="8">
         <v>0</v>
@@ -1889,7 +1869,7 @@
         <v>1600</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1998,7 +1978,7 @@
       <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="49">
         <v>1150000</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -2023,7 +2003,7 @@
     </row>
     <row r="3" spans="1:11" ht="167.25">
       <c r="A3" s="14" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>20</v>
@@ -2031,12 +2011,12 @@
       <c r="C3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="36"/>
+      <c r="D3" s="50"/>
       <c r="E3" s="6" t="s">
         <v>62</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
@@ -2045,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
@@ -2053,7 +2033,7 @@
     </row>
     <row r="4" spans="1:11" ht="60.75">
       <c r="A4" s="14" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>20</v>
@@ -2061,7 +2041,7 @@
       <c r="C4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="36"/>
+      <c r="D4" s="50"/>
       <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
@@ -2075,7 +2055,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
@@ -2083,7 +2063,7 @@
     </row>
     <row r="5" spans="1:11" ht="76.5">
       <c r="A5" s="14" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>20</v>
@@ -2091,12 +2071,12 @@
       <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
@@ -2105,7 +2085,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
         <v>25</v>
@@ -2113,22 +2093,22 @@
     </row>
     <row r="6" spans="1:11" ht="45.75">
       <c r="A6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="52">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="38">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -2137,25 +2117,25 @@
         <v>15</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="137.25">
       <c r="A7" s="15" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
@@ -2164,25 +2144,25 @@
         <v>28</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="213">
       <c r="A8" s="15" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="39"/>
+        <v>59</v>
+      </c>
+      <c r="D8" s="53"/>
       <c r="E8" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G8" s="11">
         <v>0</v>
@@ -2191,25 +2171,25 @@
         <v>50</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="106.5">
       <c r="A9" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="40"/>
+        <v>42</v>
+      </c>
+      <c r="D9" s="54"/>
       <c r="E9" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G9" s="8">
         <v>0</v>
@@ -2218,7 +2198,7 @@
         <v>1600</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15">
@@ -2271,7 +2251,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="55" t="s">
         <v>67</v>
       </c>
       <c r="B2" t="s">
@@ -2282,7 +2262,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="41"/>
+      <c r="A3" s="55"/>
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -2291,7 +2271,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="41"/>
+      <c r="A4" s="55"/>
       <c r="B4" t="s">
         <v>71</v>
       </c>
@@ -2300,7 +2280,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="56" t="s">
         <v>73</v>
       </c>
       <c r="B5" t="s">
@@ -2311,7 +2291,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="42"/>
+      <c r="A6" s="56"/>
       <c r="B6" t="s">
         <v>76</v>
       </c>
@@ -2320,7 +2300,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="42"/>
+      <c r="A7" s="56"/>
       <c r="B7" t="s">
         <v>78</v>
       </c>
@@ -2329,16 +2309,16 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="42"/>
+      <c r="A8" s="56"/>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="42"/>
+      <c r="A9" s="56"/>
       <c r="B9" t="s">
         <v>62</v>
       </c>
@@ -2347,18 +2327,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="57" t="s">
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="43"/>
+      <c r="A11" s="57"/>
       <c r="B11" t="s">
         <v>84</v>
       </c>
@@ -2367,29 +2347,29 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="58" t="s">
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="44"/>
+      <c r="A13" s="58"/>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="44"/>
+      <c r="A14" s="58"/>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
         <v>89</v>
@@ -2429,6 +2409,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2677,7 +2666,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2688,23 +2677,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BBB17A7-BDD0-4B44-881E-B1716FC76EE9}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
--- a/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blin.berdoniqi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{4DE356E2-5E12-4618-9FFB-C2B3968440F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86EDD422-57B0-45E4-A174-0EE571381309}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{4DE356E2-5E12-4618-9FFB-C2B3968440F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21CCE784-1D30-4709-9BD2-2F84153EDC84}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="105">
   <si>
     <t>Project ID</t>
   </si>
@@ -74,10 +74,7 @@
     <t>Gender (% female)</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
+    <t>VF or Non-VF</t>
   </si>
   <si>
     <t>Tag</t>
@@ -98,7 +95,13 @@
     <t>Indirect Taxonomy</t>
   </si>
   <si>
-    <t>00124574</t>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>Policy Population</t>
   </si>
   <si>
     <t>Strengthening Local Climate Action</t>
@@ -122,15 +125,15 @@
     <t>Non-VF</t>
   </si>
   <si>
+    <t>Solar</t>
+  </si>
+  <si>
     <t>Close the gap on energy access</t>
   </si>
   <si>
     <t>Renewable Energy</t>
   </si>
   <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
     <t xml:space="preserve"># of EV chargers </t>
   </si>
   <si>
@@ -159,9 +162,6 @@
   </si>
   <si>
     <t>100 Highschoolers students have been participating in the awareness campaign and capacity building programs for Renewable Energy Systems with a special focus on Solar Energy.</t>
-  </si>
-  <si>
-    <t>00130766</t>
   </si>
   <si>
     <r>
@@ -190,48 +190,66 @@
     <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
   </si>
   <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t># of people trained</t>
+  </si>
+  <si>
+    <t>Member of Climate Change Council trained for NDC development</t>
+  </si>
+  <si>
+    <t>Education Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A training program for solar installers has attracted individuals interested in energy activities. The program aimed to equip participants with the necessary skills for solar system installation. Out of the 35 individuals who enrolled in the training, 28 individuals successfully completed the program and earned their certification in solar system installation. </t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t># of companies trained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The green business accelerator, Boost x Kosovo, has successfully trained over 130 individuals and 50 companies in various aspects of sustainable practices. This program aims to accelerate the growth of green businesses and promote environmentally friendly initiatives. As a result, 32 participants were awarded grants totaling 332,000 euros. These grants will be utilized to support and enhance green transformation projects, such as the implementation of solar systems, biomass utilization, energy efficiency improvements, and more. </t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t># of individuals trained</t>
+  </si>
+  <si>
+    <t>The Earth Day campaigns and Energy Efficiency Campaigns successfully reached out to a wide audience, engaging at least 1600 individuals. These initiatives aimed to raise awareness about environmental conservation and the importance of energy efficiency.</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>00124574</t>
+  </si>
+  <si>
+    <t>00124575</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>00124576</t>
+  </si>
+  <si>
+    <t>00124577</t>
+  </si>
+  <si>
+    <t>00130766</t>
+  </si>
+  <si>
     <t>Capacity Training</t>
   </si>
   <si>
-    <t># of people trained</t>
-  </si>
-  <si>
-    <t>Member of Climate Change Council trained for NDC development</t>
-  </si>
-  <si>
-    <t>Education Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A training program for solar installers has attracted individuals interested in energy activities. The program aimed to equip participants with the necessary skills for solar system installation. Out of the 35 individuals who enrolled in the training, 28 individuals successfully completed the program and earned their certification in solar system installation. </t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t># of companies trained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The green business accelerator, Boost x Kosovo, has successfully trained over 130 individuals and 50 companies in various aspects of sustainable practices. This program aims to accelerate the growth of green businesses and promote environmentally friendly initiatives. As a result, 32 participants were awarded grants totaling 332,000 euros. These grants will be utilized to support and enhance green transformation projects, such as the implementation of solar systems, biomass utilization, energy efficiency improvements, and more. </t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t># of individuals trained</t>
-  </si>
-  <si>
-    <t>The Earth Day campaigns and Energy Efficiency Campaigns successfully reached out to a wide audience, engaging at least 1600 individuals. These initiatives aimed to raise awareness about environmental conservation and the importance of energy efficiency.</t>
-  </si>
-  <si>
-    <t>00124575</t>
-  </si>
-  <si>
-    <t>00124576</t>
-  </si>
-  <si>
-    <t>00124577</t>
-  </si>
-  <si>
     <t>00130767</t>
   </si>
   <si>
@@ -256,58 +274,73 @@
     <t>For any target with an indicator "# of systems installed", this will need a conversion to beneficiaries listed in the notes. Or, you can provide the capacity installed in MW</t>
   </si>
   <si>
-    <t>Tier</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
-    <t>Access to Energy</t>
-  </si>
-  <si>
     <t>Electricity Access</t>
   </si>
   <si>
-    <t>Access to electricity (direct access to electricity, lighting,  heating, cooling etc.)</t>
-  </si>
-  <si>
-    <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
+    <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
+  </si>
+  <si>
+    <t>Number of MW installed capacity</t>
   </si>
   <si>
     <t>Clean Cooking</t>
   </si>
   <si>
-    <t>Access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.)</t>
-  </si>
-  <si>
-    <t>Productive Use of Energy</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>Access to agricultural energy services (irrigation with solar pumps, heating systems for processing food, etc. )</t>
+    <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
+  </si>
+  <si>
+    <t>Clean Heating</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
+  </si>
+  <si>
+    <t>Agriculture and Food System</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean, affordable, and sustainable electricity for agricultural and food system activities (direct access to power machines for crop, processing, milling, grinding, de-husking, pressing, canning, sealing and packaging electricity, heating, cooling, solar water pumping for irrigation etc.) </t>
   </si>
   <si>
     <t>Health Services</t>
   </si>
   <si>
-    <t>Access to health services powered by solar PV and energy efficient systems such as hospitals</t>
+    <t>Number of people who gain access to health care facilities (direct access to electricity and heating systems for clinics, hospitals, health centers etc.) </t>
   </si>
   <si>
     <t>Water Services</t>
   </si>
   <si>
-    <t>Access to solar water pumps</t>
-  </si>
-  <si>
-    <t>Access to education services trough clean energy systems</t>
+    <t>Number of people who gain access to water services (powering water pumps, water distributions, waste management, etc.).  </t>
+  </si>
+  <si>
+    <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
   </si>
   <si>
     <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
   </si>
   <si>
-    <t>Market Development</t>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support for the development of market ecosystem </t>
   </si>
   <si>
     <t>Support for the development of medium enterprises in the energy transition market</t>
@@ -319,25 +352,22 @@
     <t>Support for the development of small enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Capacity Building</t>
-  </si>
-  <si>
-    <t>Individuals who participate in trainings for energy activities</t>
+    <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
   </si>
   <si>
     <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
   </si>
   <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
+  </si>
+  <si>
     <t>Individuals who participate in advocacy and campaign on energy</t>
   </si>
   <si>
-    <t>Policy and Regulator Frameworks</t>
-  </si>
-  <si>
-    <t>Policy or Regulatory Framework</t>
-  </si>
-  <si>
-    <t>Policies and regulatory framework can have far-reaching impacts on the energy access situation in countries</t>
+    <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
   </si>
   <si>
     <t>Other</t>
@@ -356,12 +386,18 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -437,49 +473,26 @@
       <name val="Helvetica Neue"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFFFFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FFFFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42FFFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00E1DA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00DAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00BDB7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -499,8 +512,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -588,177 +607,422 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1066,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C58D4B-AF56-46AC-89E7-4807C4DC4588}">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -1078,431 +1342,539 @@
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" customWidth="1"/>
     <col min="9" max="9" width="36.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
     <col min="11" max="11" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="47.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.75">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:28" ht="18.75">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="69" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="106.5">
-      <c r="A2" s="14" t="s">
+      <c r="T1" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="U1" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:28" ht="106.5">
+      <c r="A2" s="39">
+        <v>124574</v>
+      </c>
+      <c r="B2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="36">
+      <c r="C2" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="27">
         <v>1220000</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="6">
+      <c r="F2" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="26">
         <v>0</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="26">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I2" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="26"/>
-      <c r="L2" s="27" t="s">
+      <c r="J2" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25" t="s">
+      <c r="K2" s="30"/>
+      <c r="L2" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="M2" s="22"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-    </row>
-    <row r="3" spans="1:19" ht="167.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="6" t="s">
+      <c r="T2" s="22"/>
+      <c r="U2" s="72"/>
+      <c r="X2" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="AB2" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="6">
+    </row>
+    <row r="3" spans="1:28" ht="167.25">
+      <c r="A3" s="41"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="91" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="91">
         <v>0</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="91">
         <v>2</v>
       </c>
-      <c r="I3" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="27" t="s">
+      <c r="I3" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25" t="s">
+      <c r="K3" s="29"/>
+      <c r="L3" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="72"/>
+      <c r="X3" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y3" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-    </row>
-    <row r="4" spans="1:19" ht="60.75">
-      <c r="A4" s="14"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="AB3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="6">
+    </row>
+    <row r="4" spans="1:28" ht="60.75">
+      <c r="A4" s="45"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="26">
         <v>0</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="26">
         <v>0.04</v>
       </c>
-      <c r="I4" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="25"/>
-      <c r="L4" s="27" t="s">
+      <c r="I4" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25" t="s">
+      <c r="K4" s="29"/>
+      <c r="L4" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="25" t="s">
+      <c r="M4" s="22"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-    </row>
-    <row r="5" spans="1:19" ht="76.5">
-      <c r="A5" s="14"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="T4" s="22"/>
+      <c r="U4" s="72"/>
+      <c r="X4" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB4" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="76.5">
+      <c r="A5" s="47"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="6">
+      <c r="F5" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="26">
         <v>0</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="26">
         <v>100</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="I5" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="29"/>
+      <c r="L5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="72"/>
+      <c r="X5" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+    </row>
+    <row r="6" spans="1:28" ht="45.75">
+      <c r="A6" s="53">
+        <v>130766</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="56">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="26">
+        <v>0</v>
+      </c>
+      <c r="H6" s="26">
+        <v>15</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="72"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB6" s="29"/>
+    </row>
+    <row r="7" spans="1:28" ht="137.25">
+      <c r="A7" s="41"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="26">
+        <v>0</v>
+      </c>
+      <c r="H7" s="26">
+        <v>28</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="22"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="72"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+    </row>
+    <row r="8" spans="1:28" ht="213">
+      <c r="A8" s="89"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="33">
+        <v>0</v>
+      </c>
+      <c r="H8" s="32">
+        <v>50</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="22"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="72"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" s="89"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="35"/>
+      <c r="H9" s="26">
+        <v>130</v>
+      </c>
+      <c r="I9" s="34"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="22"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="72"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+    </row>
+    <row r="10" spans="1:28" ht="106.5">
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="25"/>
-      <c r="L5" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-    </row>
-    <row r="6" spans="1:19" ht="45.75">
-      <c r="A6" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="36">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="G10" s="26">
         <v>0</v>
       </c>
-      <c r="H6" s="8">
-        <v>15</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-    </row>
-    <row r="7" spans="1:19" ht="137.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>28</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-    </row>
-    <row r="8" spans="1:19" ht="213">
-      <c r="A8" s="39"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0</v>
-      </c>
-      <c r="H8" s="23">
-        <v>50</v>
-      </c>
-      <c r="I8" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="8">
-        <v>130</v>
-      </c>
-      <c r="I9" s="32"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-    </row>
-    <row r="10" spans="1:19" ht="106.5">
-      <c r="A10" s="15"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="H10" s="26">
         <v>1600</v>
       </c>
-      <c r="I10" s="33" t="s">
+      <c r="I10" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-    </row>
-    <row r="13" spans="1:19">
-      <c r="A13" s="18"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="22"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="72"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-  </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S10 T2" xr:uid="{BD3517BF-52CE-4CBD-A829-6DE6E456AA70}">
-      <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R10" xr:uid="{1903FAFB-16C1-493F-902E-086D0A26FC89}">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q10" xr:uid="{1903FAFB-16C1-493F-902E-086D0A26FC89}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q10" xr:uid="{95C10871-6C7A-4942-A0EE-D668A6751D1A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P10" xr:uid="{95C10871-6C7A-4942-A0EE-D668A6751D1A}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P10" xr:uid="{47C99ACA-9AF7-4987-985D-C08C8F1856A2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB10" xr:uid="{47C99ACA-9AF7-4987-985D-C08C8F1856A2}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O10" xr:uid="{B9D23206-497E-43DF-A66B-8DB80A9212E4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA10 N2:N10" xr:uid="{B9D23206-497E-43DF-A66B-8DB80A9212E4}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{13C3CF28-FAF8-48E2-A604-542D4D7B233A}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O10" xr:uid="{0D0DA9D4-76F3-4A9C-9A3E-36FF6EF57CCE}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L10" xr:uid="{8A88A346-3078-469C-9B4E-8D6BCC2AEFED}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M10" xr:uid="{D9DE5EA4-161C-4DB0-9DD0-2453ADBA21DB}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T10" xr:uid="{C4B0DEC4-AFB0-49D6-85A4-DD3F5B413C3D}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R10" xr:uid="{F4146B98-99BD-4254-8326-AD8A99F3548C}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S10" xr:uid="{C2369686-0951-4D0B-8C14-5F9567A840D5}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" location=":~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka" xr:uid="{87F04B92-BD13-43DB-9904-327B77C6CF0B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E575982D-1141-4F33-9D4B-D4F82D4DE160}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D47DB21-3845-459D-8A7B-6215FB039FF1}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2 E4:E10</xm:sqref>
+          <xm:sqref>E2:E10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1530,350 +1902,350 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="16" t="s">
+      <c r="L1" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="Q1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="R1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="S1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="16" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="2" spans="1:19" ht="106.5">
-      <c r="A2" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="A2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="43">
+      <c r="C2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="73">
         <v>1150000</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="14"/>
+      <c r="L2" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="18"/>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="167.25">
+      <c r="A3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D3" s="74"/>
+      <c r="E3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="60.75">
+      <c r="A4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="74"/>
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="6">
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="3">
         <v>0</v>
       </c>
-      <c r="H2" s="6">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="20" t="s">
+      <c r="H4" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="21"/>
-      <c r="O2" t="s">
+      <c r="L4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="P2" t="s">
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="76.5">
+      <c r="A5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="75"/>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="45.75">
+      <c r="A6" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="76">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>15</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="137.25">
+      <c r="A7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="77"/>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="167.25">
-      <c r="A3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="I7" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="213">
+      <c r="A8" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="77"/>
+      <c r="E8" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="21">
         <v>0</v>
       </c>
-      <c r="H3" s="6">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="60.75">
-      <c r="A4" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="H8" s="20">
+        <v>50</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="80"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="5">
+        <v>130</v>
+      </c>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" spans="1:19" ht="106.5">
+      <c r="A10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="78"/>
+      <c r="E10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="5">
         <v>0</v>
       </c>
-      <c r="H4" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="76.5">
-      <c r="A5" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>100</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="45.75">
-      <c r="A6" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="46">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>15</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="137.25">
-      <c r="A7" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>28</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="213">
-      <c r="A8" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0</v>
-      </c>
-      <c r="H8" s="23">
-        <v>50</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="8">
-        <v>130</v>
-      </c>
-      <c r="I9" s="13"/>
-    </row>
-    <row r="10" spans="1:19" ht="106.5">
-      <c r="A10" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="H10" s="5">
         <v>1600</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="18"/>
+      <c r="A13" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1883,7 +2255,7 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{F9A91EB7-214F-48FA-912C-2CFFE3B8FB02}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O10" xr:uid="{D4B41F5B-510A-4182-AC10-33041A2418B1}">
@@ -1909,7 +2281,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D5106D0-8AA4-49C7-95D6-58507C7E90F4}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>E2 E4:E10</xm:sqref>
         </x14:dataValidation>
@@ -1937,273 +2309,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="106.5">
-      <c r="A2" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="A2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="49">
+      <c r="C2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="83">
         <v>1150000</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" spans="1:11" ht="167.25">
+      <c r="A3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D3" s="84"/>
+      <c r="E3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60.75">
+      <c r="A4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="84"/>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="76.5">
+      <c r="A5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="85"/>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45.75">
+      <c r="A6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="6">
+      <c r="B6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="86">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="17"/>
-    </row>
-    <row r="3" spans="1:11" ht="167.25">
-      <c r="A3" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="H6" s="5">
+        <v>15</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="137.25">
+      <c r="A7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="87"/>
+      <c r="E7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="H3" s="6">
-        <v>2</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60.75">
-      <c r="A4" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="H7" s="5">
+        <v>28</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="213">
+      <c r="A8" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="87"/>
+      <c r="E8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="8">
         <v>0</v>
       </c>
-      <c r="H4" s="6">
-        <v>3</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="76.5">
-      <c r="A5" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="H8" s="5">
+        <v>50</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="106.5">
+      <c r="A9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="88"/>
+      <c r="E9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="6">
+      <c r="F9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="5">
         <v>0</v>
       </c>
-      <c r="H5" s="6">
-        <v>100</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="45.75">
-      <c r="A6" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="52">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>15</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="137.25">
-      <c r="A7" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>28</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="213">
-      <c r="A8" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8">
-        <v>50</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="106.5">
-      <c r="A9" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="H9" s="5">
         <v>1600</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15">
-      <c r="A12" s="18" t="s">
-        <v>64</v>
+      <c r="A12" s="15" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2211,7 +2583,7 @@
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="D6:D9"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -2219,7 +2591,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BF404E26-67A6-40D5-A4BB-66ACDC63AFDF}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E9</xm:sqref>
         </x14:dataValidation>
@@ -2231,190 +2603,203 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="52.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" customWidth="1"/>
-    <col min="3" max="3" width="96" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B1" s="64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30.75">
+      <c r="A2" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="92" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="45.75">
+      <c r="A6" s="92" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30.75">
+      <c r="A7" s="92" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30.75">
+      <c r="A8" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30.75">
+      <c r="A9" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="92" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="93" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="92" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="93" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30.75">
+      <c r="A12" s="92" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="55"/>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="55"/>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="56"/>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="56"/>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="56"/>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="56"/>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B13" s="93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="57"/>
-      <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B15" s="93" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="92" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="93" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="58"/>
-      <c r="B13" t="s">
+      <c r="B17" s="65" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="58"/>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
+      <c r="B18" s="93" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="45.75">
+      <c r="A19" s="92" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="93" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="93" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30.75">
+      <c r="A21" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="94" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="93" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2667,18 +3052,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2686,5 +3069,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
--- a/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28521"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\blin.berdoniqi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{4DE356E2-5E12-4618-9FFB-C2B3968440F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21CCE784-1D30-4709-9BD2-2F84153EDC84}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{4DE356E2-5E12-4618-9FFB-C2B3968440F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8ED81007-D054-4B7E-A1FA-23857DB8F8BD}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="5" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="4" r:id="rId2"/>
-    <sheet name="Projects- UNDP KOSOVO" sheetId="3" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Projects- UNDP KOSOVO" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="133">
   <si>
     <t>Project ID</t>
   </si>
@@ -104,34 +104,291 @@
     <t>Policy Population</t>
   </si>
   <si>
+    <t>Project Document</t>
+  </si>
+  <si>
     <t>Strengthening Local Climate Action</t>
   </si>
   <si>
+    <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>3 PV systems installed (127.36 MWh/year)</t>
+  </si>
+  <si>
+    <t>Three PV systems were installed on public buildings in the two municipalities of Prizren (1) and Suharekë/Suva Reka (2) as per October 2024. The total capacity of the 3 systems installed in both capacities is 98.8 kWp, generating 127.36 MWh annually, and reducing CO2 emissions by 3970.17 tons.</t>
+  </si>
+  <si>
+    <t>Austrian Development Agency</t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>5 small-scale PV systems installed (44.58 MWh/year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As part of an initiative to provide in kind support to women-led MSMEs to green their business through energy-efficient measures, 5 small-scale PV systems with battery storage were installed. The total capacity of the 5 systems installed in both capacities is 36.58 kWp, generating 44.94 MWh annually and reducing CO2 emissions by 20.12 tons total per year over the lifetime of the systems (low number due to LCA of batteries that make up the system)</t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t># of people reached</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 DC EV charger was installed in the municipality of Suharekë/Suva Reka. This charging station provides convenient access to sustainable and clean energy for EV owners within the municipality. This initiative contributes to reducing carbon emissions and encourages the use of environmentally friendly transportation options in Prizren. We estimate the number of people benefiting from using this charging station over one year (direct beneficiaries), including the visiting diaspora, at 700. </t>
+  </si>
+  <si>
+    <t>to the CO: Please estimate number of beneficiaries.</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t># of people trained</t>
+  </si>
+  <si>
+    <t>44 municipal officials (25% women and 75% men) were trained in understanding climate change initiatives, GHG inventories and in distinguishing between emission reduction and adaptation efforts and strategies.</t>
+  </si>
+  <si>
+    <t>25% female participant rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t>140'000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 main Investment Opportunity Areas for Prizren and for Suharekë/Suva Reka municipalities were identified and a respective report published. Potential beneficiares of these investment projects (if realized) include the total populations of both Prizren and SR
+Area 1: Renewable Energy Powered District Heating System 
+Area 2: Rooftop Solar Power Generation Investment  
+Area 3: Electrification of Public Transportation </t>
+  </si>
+  <si>
+    <t>41 students of Prizren University "Ukshin Hoti" attained certificates for attending a mentorship programme with the focus topics of climate change and green development (22 female (54 %) and 19 male (46 %)</t>
+  </si>
+  <si>
+    <t>54% female participant rate</t>
+  </si>
+  <si>
+    <t>Campaign Participant</t>
+  </si>
+  <si>
+    <t>100 Highschool students from 4 high schools in Prizren and Suharekë/Suva Reka, participated in an awareness campaign and thus gained knowledge on clean energy and sustainable energy practices</t>
+  </si>
+  <si>
+    <t>20% female participant rate</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kosovo Climate Promise Project 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - "Climate Promise Kosovo – From Pledge to Impact (CP2 Project)"</t>
+    </r>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/01000987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Members of the Kosovo Climate Change (KCCC) Council as well as from the Working Group to develop the voluntary NDC of Kosovo underwent several rounds of capacity-building activities that focused on the development process of v-NDCs, the structure of v-NDCs, data collection process, reporting and monitoring process of the V-NDC. </t>
+  </si>
+  <si>
+    <t>Sida (Swedish International Development Cooperation Agency)</t>
+  </si>
+  <si>
+    <t>30% female participation</t>
+  </si>
+  <si>
+    <t>The first inclusive voluntary NDC for Kosovo was developed with major support of UNDP, currently being prepared for public consultations as of October 2024. The measures outlined in the NDC could have a major impact and contribute significantly to the green transition and climate mitigation efforts of Kosovo. The approximate number of people reached (indirect beneficiaires) is estimated at 810,000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 SMEs operating in sectors such as fashion, agriculture, circular economy, and energy efficiency received training through the UNDP Acceleration programme "BOOST x Kosovo: Next Gen". Following the completion of the program, 28 companies fulfilled all the criteria and graduated from BOOST x Kosovo. From these graduates, the 12 most promising ideas were chosen to implement their solutions. As a result, the SMEs were able to integrate into their business operation technologies such as smart energy solutions and the electrification of their means of transport through charging stations. Through the green solutions implemented, an estimated 100 new green job opportunities were created. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The project successfully delivered a master course for trainers of solar pannel installers, where 5 Vocational Training Centres participated. The training module (for the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Solar Panel Technician</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> profile) is in the process of receiving validation by the Ministry of Education, Science, Technology and Innovation (MESTI) as of November 2024. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5 trainers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> received certification, and for the academic year 2024 they are currently training </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">85 students </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to become future PV Technicians in their respective VTCs (5) across Kosovo.</t>
+    </r>
+  </si>
+  <si>
+    <t>20% potential female participation (guesstimate)</t>
+  </si>
+  <si>
+    <t>Implementation of UNDP Kosovo public awareness campaign on climate action and environmental engagement and implementation of Earth Days (Kosovo Office traditional campaign), reaching a wide audience and engaging at least 1500 individuals. These initiatives aimed to raise awareness about environmental conservation and the importance of energy efficiency.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Climate Promise Project-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "Growth Through Green and Rapid Recovery from Covid-19"</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://climatepromise.undp.org/what-we-do/where-we-work/kosovo </t>
+  </si>
+  <si>
+    <t>Member of Climate Change Council trained for NDC development</t>
+  </si>
+  <si>
+    <t>Education Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A training program for solar installers has attracted individuals interested in energy activities. The program aimed to equip participants with the necessary skills for solar system installation. Out of the 35 individuals who enrolled in the training, 28 individuals successfully completed the program and earned their certification in solar system installation. </t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t># of companies trained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The green business accelerator, Boost x Kosovo, has successfully trained over 130 individuals and 50 companies in various aspects of sustainable practices. This program aims to accelerate the growth of green businesses and promote environmentally friendly initiatives. As a result, 32 participants were awarded grants totaling 332,000 euros. These grants will be utilized to support and enhance green transformation projects, such as the implementation of solar systems, biomass utilization, energy efficiency improvements, and more. </t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t># of individuals trained</t>
+  </si>
+  <si>
+    <t>The Earth Day campaigns and Energy Efficiency Campaigns successfully reached out to a wide audience, engaging at least 1600 individuals. These initiatives aimed to raise awareness about environmental conservation and the importance of energy efficiency.</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>00124574</t>
+  </si>
+  <si>
     <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
   </si>
   <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
     <t>systems installed MW</t>
   </si>
   <si>
     <t xml:space="preserve">Access to energy in the Municipality of Prizren has been enhanced through the installation of renewable energy capacity, specifically solar photovoltaic (PV) systems. As of 2022, one such system has been successfully installed in a public building. </t>
   </si>
   <si>
-    <t>Austrian Development Agency</t>
-  </si>
-  <si>
-    <t>Non-VF</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Renewable Energy</t>
+    <t>00124575</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
   </si>
   <si>
     <t xml:space="preserve"># of EV chargers </t>
@@ -140,13 +397,7 @@
     <t>In the municipality of Prizren we have been working in promoting electric vehicle (EV) adoption by installing two EV charging systems. These charging stations provide convenient access to sustainable and clean energy for EV owners within the municipality. This initiative contributes to reducing carbon emissions and encourages the use of environmentally friendly transportation options in Prizren.</t>
   </si>
   <si>
-    <t>to the CO: Please estimate number of beneficiaries.</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>Energy Efficiency</t>
+    <t>00124576</t>
   </si>
   <si>
     <t>3 systems installed 125.93 MWh/year) MW</t>
@@ -155,13 +406,13 @@
     <t xml:space="preserve">In 2023, three solar photovoltaic (PV) systems will be installed in public buildings, benefiting the municipalities of Prizren and Suhareka. </t>
   </si>
   <si>
-    <t>Campaign Participant</t>
-  </si>
-  <si>
-    <t># of people reached</t>
+    <t>00124577</t>
   </si>
   <si>
     <t>100 Highschoolers students have been participating in the awareness campaign and capacity building programs for Renewable Energy Systems with a special focus on Solar Energy.</t>
+  </si>
+  <si>
+    <t>00130766</t>
   </si>
   <si>
     <r>
@@ -190,63 +441,6 @@
     <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
   </si>
   <si>
-    <t>Capacity Building Training</t>
-  </si>
-  <si>
-    <t># of people trained</t>
-  </si>
-  <si>
-    <t>Member of Climate Change Council trained for NDC development</t>
-  </si>
-  <si>
-    <t>Education Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A training program for solar installers has attracted individuals interested in energy activities. The program aimed to equip participants with the necessary skills for solar system installation. Out of the 35 individuals who enrolled in the training, 28 individuals successfully completed the program and earned their certification in solar system installation. </t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t># of companies trained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The green business accelerator, Boost x Kosovo, has successfully trained over 130 individuals and 50 companies in various aspects of sustainable practices. This program aims to accelerate the growth of green businesses and promote environmentally friendly initiatives. As a result, 32 participants were awarded grants totaling 332,000 euros. These grants will be utilized to support and enhance green transformation projects, such as the implementation of solar systems, biomass utilization, energy efficiency improvements, and more. </t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t># of individuals trained</t>
-  </si>
-  <si>
-    <t>The Earth Day campaigns and Energy Efficiency Campaigns successfully reached out to a wide audience, engaging at least 1600 individuals. These initiatives aimed to raise awareness about environmental conservation and the importance of energy efficiency.</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>00124574</t>
-  </si>
-  <si>
-    <t>00124575</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>00124576</t>
-  </si>
-  <si>
-    <t>00124577</t>
-  </si>
-  <si>
-    <t>00130766</t>
-  </si>
-  <si>
     <t>Capacity Training</t>
   </si>
   <si>
@@ -316,9 +510,6 @@
     <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
   </si>
   <si>
-    <t>Transportation and E-mobility Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
   </si>
   <si>
@@ -335,9 +526,6 @@
   </si>
   <si>
     <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financing support </t>
   </si>
   <si>
     <t xml:space="preserve">Support for the development of market ecosystem </t>
@@ -386,7 +574,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,6 +674,20 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -514,12 +716,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -596,116 +798,12 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -723,19 +821,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -748,13 +833,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -814,150 +990,161 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1006,13 +1193,7 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1026,8 +1207,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1330,12 +1511,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C58D4B-AF56-46AC-89E7-4807C4DC4588}">
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
     <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.140625" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="26.42578125" customWidth="1"/>
     <col min="6" max="6" width="22.5703125" customWidth="1"/>
@@ -1345,525 +1526,957 @@
     <col min="10" max="10" width="28" customWidth="1"/>
     <col min="11" max="11" width="14.28515625" customWidth="1"/>
     <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="20" customWidth="1"/>
     <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.140625" customWidth="1"/>
+    <col min="22" max="22" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.75">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="67" t="s">
+      <c r="M1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="67" t="s">
+      <c r="P1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="67" t="s">
+      <c r="Q1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="68" t="s">
+      <c r="R1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="69" t="s">
+      <c r="S1" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="68" t="s">
+      <c r="T1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="69" t="s">
+      <c r="U1" s="31" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" ht="106.5">
-      <c r="A2" s="39">
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="121.5">
+      <c r="A2" s="42">
         <v>124574</v>
       </c>
-      <c r="B2" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="90" t="s">
+      <c r="B2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="27">
+      <c r="C2" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="68">
         <v>1220000</v>
       </c>
-      <c r="E2" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="E2" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="26">
+      <c r="F2" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="43">
         <v>0</v>
       </c>
-      <c r="H2" s="26">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="29" t="s">
+      <c r="H2" s="43">
+        <v>0.01</v>
+      </c>
+      <c r="I2" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="30"/>
-      <c r="L2" s="70" t="s">
+      <c r="J2" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="22"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="22"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="38"/>
+      <c r="N2" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>30</v>
+      </c>
       <c r="P2" s="22"/>
       <c r="Q2" s="22"/>
       <c r="R2" s="22"/>
-      <c r="S2" s="72" t="s">
+      <c r="S2" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="22"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="22"/>
-      <c r="U2" s="72"/>
-      <c r="X2" s="22" t="s">
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB2" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="183">
+      <c r="A3" s="48"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29" t="s">
+      <c r="K3" s="14"/>
+      <c r="L3" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="38"/>
+      <c r="N3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="AB2" s="29" t="s">
+      <c r="O3" s="22" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" ht="167.25">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="91" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="91">
-        <v>0</v>
-      </c>
-      <c r="H3" s="91">
-        <v>2</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="22"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="22"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="R3" s="22"/>
-      <c r="S3" s="72"/>
+      <c r="S3" s="33" t="s">
+        <v>31</v>
+      </c>
       <c r="T3" s="22"/>
-      <c r="U3" s="72"/>
-      <c r="X3" s="22" t="s">
+      <c r="U3" s="33"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="23"/>
+    </row>
+    <row r="4" spans="1:28" ht="213">
+      <c r="A4" s="48"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="14">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14">
+        <v>700</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB3" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" ht="60.75">
-      <c r="A4" s="45"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="26">
-        <v>0</v>
-      </c>
-      <c r="H4" s="26">
-        <v>0.04</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="29"/>
-      <c r="L4" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="22"/>
-      <c r="N4" s="71"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="38"/>
+      <c r="N4" s="32"/>
       <c r="O4" s="22"/>
       <c r="P4" s="22"/>
       <c r="Q4" s="22"/>
       <c r="R4" s="22"/>
-      <c r="S4" s="72" t="s">
+      <c r="S4" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="22"/>
+      <c r="U4" s="33"/>
+      <c r="X4" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="T4" s="22"/>
-      <c r="U4" s="72"/>
-      <c r="X4" s="22" t="s">
+      <c r="Y4" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB4" s="23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="91.5">
+      <c r="A5" s="48"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14">
+        <v>32</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB4" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" ht="76.5">
-      <c r="A5" s="47"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="26">
-        <v>0</v>
-      </c>
-      <c r="H5" s="26">
-        <v>100</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="22"/>
-      <c r="N5" s="71"/>
+      <c r="K5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="38"/>
+      <c r="N5" s="32"/>
       <c r="O5" s="22"/>
       <c r="P5" s="22"/>
       <c r="Q5" s="22"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="72"/>
+      <c r="S5" s="33"/>
       <c r="T5" s="22"/>
-      <c r="U5" s="72"/>
-      <c r="X5" s="22" t="s">
+      <c r="U5" s="33"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+    </row>
+    <row r="6" spans="1:28" ht="213">
+      <c r="A6" s="48"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-    </row>
-    <row r="6" spans="1:28" ht="45.75">
-      <c r="A6" s="53">
-        <v>130766</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="56">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="26">
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>15</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="22"/>
-      <c r="N6" s="71"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="38"/>
+      <c r="N6" s="32"/>
       <c r="O6" s="22"/>
       <c r="P6" s="22"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22"/>
-      <c r="S6" s="72"/>
+      <c r="S6" s="33"/>
       <c r="T6" s="22"/>
-      <c r="U6" s="72"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB6" s="29"/>
-    </row>
-    <row r="7" spans="1:28" ht="137.25">
-      <c r="A7" s="41"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="U6" s="33"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="23"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
+    </row>
+    <row r="7" spans="1:28" ht="91.5">
+      <c r="A7" s="48"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="14">
         <v>0</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="14">
+        <v>41</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="22"/>
-      <c r="N7" s="71"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="32"/>
       <c r="O7" s="22"/>
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="R7" s="22"/>
-      <c r="S7" s="72"/>
+      <c r="S7" s="33"/>
       <c r="T7" s="22"/>
-      <c r="U7" s="72"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-    </row>
-    <row r="8" spans="1:28" ht="213">
-      <c r="A8" s="89"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="59"/>
+      <c r="U7" s="33"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="23"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
+    </row>
+    <row r="8" spans="1:28" ht="91.5">
+      <c r="A8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="33">
+        <v>50</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="51">
         <v>0</v>
       </c>
-      <c r="H8" s="32">
-        <v>50</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="70" t="s">
+      <c r="H8" s="51">
+        <v>100</v>
+      </c>
+      <c r="I8" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="M8" s="22"/>
-      <c r="N8" s="71"/>
+      <c r="K8" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="38"/>
+      <c r="N8" s="32"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="R8" s="22"/>
-      <c r="S8" s="72"/>
+      <c r="S8" s="33"/>
       <c r="T8" s="22"/>
-      <c r="U8" s="72"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
+      <c r="U8" s="33"/>
+      <c r="X8" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="89"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="26">
-        <v>130</v>
-      </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="22"/>
-      <c r="N9" s="71"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="32"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="R9" s="22"/>
-      <c r="S9" s="72"/>
+      <c r="S9" s="33"/>
       <c r="T9" s="22"/>
-      <c r="U9" s="72"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-    </row>
-    <row r="10" spans="1:28" ht="106.5">
-      <c r="A10" s="47"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="26">
+      <c r="U9" s="33"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+    </row>
+    <row r="10" spans="1:28" ht="137.25">
+      <c r="A10" s="42">
+        <v>1000987</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="68">
+        <v>381780</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="43">
         <v>0</v>
       </c>
-      <c r="H10" s="26">
-        <v>1600</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="22"/>
-      <c r="N10" s="71"/>
+      <c r="H10" s="43">
+        <v>30</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="38"/>
+      <c r="N10" s="32"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="R10" s="22"/>
-      <c r="S10" s="72"/>
+      <c r="S10" s="33"/>
       <c r="T10" s="22"/>
-      <c r="U10" s="72"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-    </row>
-    <row r="13" spans="1:28">
-      <c r="A13" s="15"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
+    </row>
+    <row r="11" spans="1:28" ht="167.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="73">
+        <v>810000</v>
+      </c>
+      <c r="I11" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="38"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="33"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="23"/>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="23"/>
+    </row>
+    <row r="12" spans="1:28" ht="290.25">
+      <c r="A12" s="48"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>70</v>
+      </c>
+      <c r="I12" s="94" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="38"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="33"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+    </row>
+    <row r="13" spans="1:28" ht="213">
+      <c r="A13" s="48"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>90</v>
+      </c>
+      <c r="I13" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="38"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="T13" s="22"/>
+      <c r="U13" s="33"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+    </row>
+    <row r="14" spans="1:28" ht="152.25">
+      <c r="A14" s="50"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="51">
+        <v>0</v>
+      </c>
+      <c r="H14" s="51">
+        <v>1500</v>
+      </c>
+      <c r="I14" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" s="51"/>
+      <c r="L14" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="38"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="33"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="A15" s="34"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="59"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="33"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="33"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+    </row>
+    <row r="16" spans="1:28" ht="45.75">
+      <c r="A16" s="42">
+        <v>130766</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="45">
+        <v>704052</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="43">
+        <v>0</v>
+      </c>
+      <c r="H16" s="43">
+        <v>15</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="38"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB16" s="23"/>
+    </row>
+    <row r="17" spans="1:28" ht="137.25">
+      <c r="A17" s="48"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>28</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="38"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="T17" s="22"/>
+      <c r="U17" s="33"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="23"/>
+    </row>
+    <row r="18" spans="1:28" ht="213">
+      <c r="A18" s="63"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="60">
+        <v>0</v>
+      </c>
+      <c r="H18" s="57">
+        <v>50</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="38"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="33"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
+    </row>
+    <row r="19" spans="1:28">
+      <c r="A19" s="63"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="62"/>
+      <c r="H19" s="14">
+        <v>130</v>
+      </c>
+      <c r="I19" s="61"/>
+      <c r="L19" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="38"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="33"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="23"/>
+      <c r="AA19" s="23"/>
+      <c r="AB19" s="23"/>
+    </row>
+    <row r="20" spans="1:28" ht="106.5">
+      <c r="A20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="51">
+        <v>0</v>
+      </c>
+      <c r="H20" s="51">
+        <v>1600</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="38"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="33"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="33"/>
+      <c r="X20" s="23"/>
+      <c r="Y20" s="23"/>
+      <c r="Z20" s="23"/>
+      <c r="AA20" s="23"/>
+      <c r="AB20" s="23"/>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q10" xr:uid="{1903FAFB-16C1-493F-902E-086D0A26FC89}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q20" xr:uid="{1903FAFB-16C1-493F-902E-086D0A26FC89}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P10" xr:uid="{95C10871-6C7A-4942-A0EE-D668A6751D1A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P20" xr:uid="{95C10871-6C7A-4942-A0EE-D668A6751D1A}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB10" xr:uid="{47C99ACA-9AF7-4987-985D-C08C8F1856A2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB20" xr:uid="{47C99ACA-9AF7-4987-985D-C08C8F1856A2}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA10 N2:N10" xr:uid="{B9D23206-497E-43DF-A66B-8DB80A9212E4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA20 N2:N20" xr:uid="{B9D23206-497E-43DF-A66B-8DB80A9212E4}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O10" xr:uid="{0D0DA9D4-76F3-4A9C-9A3E-36FF6EF57CCE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O20" xr:uid="{0D0DA9D4-76F3-4A9C-9A3E-36FF6EF57CCE}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L10" xr:uid="{8A88A346-3078-469C-9B4E-8D6BCC2AEFED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14:L20 L2:L4 L6 L8:L9" xr:uid="{8A88A346-3078-469C-9B4E-8D6BCC2AEFED}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M10" xr:uid="{D9DE5EA4-161C-4DB0-9DD0-2453ADBA21DB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M20" xr:uid="{D9DE5EA4-161C-4DB0-9DD0-2453ADBA21DB}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T10" xr:uid="{C4B0DEC4-AFB0-49D6-85A4-DD3F5B413C3D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T20" xr:uid="{C4B0DEC4-AFB0-49D6-85A4-DD3F5B413C3D}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R10" xr:uid="{F4146B98-99BD-4254-8326-AD8A99F3548C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R20" xr:uid="{F4146B98-99BD-4254-8326-AD8A99F3548C}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S10" xr:uid="{C2369686-0951-4D0B-8C14-5F9567A840D5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S20" xr:uid="{C2369686-0951-4D0B-8C14-5F9567A840D5}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location=":~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka" xr:uid="{87F04B92-BD13-43DB-9904-327B77C6CF0B}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{87F04B92-BD13-43DB-9904-327B77C6CF0B}"/>
+    <hyperlink ref="C10" r:id="rId2" xr:uid="{F4D843E2-5DB8-450C-A8AC-CE42180825BF}"/>
+    <hyperlink ref="C16" r:id="rId3" xr:uid="{D5FF40BD-86E3-40BC-9521-E88E2880646F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1874,7 +2487,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E10</xm:sqref>
+          <xm:sqref>E2:E20</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1936,10 +2549,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="O1" s="13" t="s">
         <v>13</v>
@@ -1959,22 +2572,22 @@
     </row>
     <row r="2" spans="1:19" ht="106.5">
       <c r="A2" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="73">
+        <v>77</v>
+      </c>
+      <c r="D2" s="78">
         <v>1150000</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -1983,18 +2596,18 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="14"/>
       <c r="L2" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="18"/>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P2" t="s">
         <v>30</v>
@@ -2002,20 +2615,20 @@
     </row>
     <row r="3" spans="1:19" ht="167.25">
       <c r="A3" s="11" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="74"/>
+        <v>77</v>
+      </c>
+      <c r="D3" s="79"/>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -2024,40 +2637,40 @@
         <v>2</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="60.75">
       <c r="A4" s="11" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="74"/>
+        <v>77</v>
+      </c>
+      <c r="D4" s="79"/>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -2066,16 +2679,16 @@
         <v>0.04</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P4" t="s">
         <v>30</v>
@@ -2083,20 +2696,20 @@
     </row>
     <row r="5" spans="1:19" ht="76.5">
       <c r="A5" s="11" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="75"/>
+        <v>77</v>
+      </c>
+      <c r="D5" s="80"/>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -2105,33 +2718,33 @@
         <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="45.75">
       <c r="A6" s="12" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="81">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="76">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -2140,28 +2753,28 @@
         <v>15</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="137.25">
       <c r="A7" s="12" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="82"/>
+      <c r="E7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" s="77"/>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -2170,25 +2783,25 @@
         <v>28</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="213">
-      <c r="A8" s="79" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="79" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="81" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="77"/>
+      <c r="A8" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="82"/>
       <c r="E8" s="19" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G8" s="21">
         <v>0</v>
@@ -2197,19 +2810,19 @@
         <v>50</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="80"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="77"/>
+      <c r="A9" s="85"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="82"/>
       <c r="E9" s="10" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="5">
@@ -2219,20 +2832,20 @@
     </row>
     <row r="10" spans="1:19" ht="106.5">
       <c r="A10" s="12" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="78"/>
+        <v>91</v>
+      </c>
+      <c r="D10" s="83"/>
       <c r="E10" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -2241,7 +2854,7 @@
         <v>1600</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2342,22 +2955,22 @@
     </row>
     <row r="2" spans="1:11" ht="106.5">
       <c r="A2" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="83">
+        <v>77</v>
+      </c>
+      <c r="D2" s="88">
         <v>1150000</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -2366,29 +2979,29 @@
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="14"/>
     </row>
     <row r="3" spans="1:11" ht="167.25">
       <c r="A3" s="11" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="84"/>
+        <v>77</v>
+      </c>
+      <c r="D3" s="89"/>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -2397,28 +3010,28 @@
         <v>2</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60.75">
       <c r="A4" s="11" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="84"/>
+        <v>77</v>
+      </c>
+      <c r="D4" s="89"/>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -2427,28 +3040,28 @@
         <v>3</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="76.5">
       <c r="A5" s="11" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="85"/>
+        <v>77</v>
+      </c>
+      <c r="D5" s="90"/>
       <c r="E5" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -2457,30 +3070,30 @@
         <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45.75">
       <c r="A6" s="12" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="91">
+        <v>704052</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="86">
-        <v>704052</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -2489,25 +3102,25 @@
         <v>15</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="137.25">
       <c r="A7" s="12" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="92"/>
+      <c r="E7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" s="87"/>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -2516,25 +3129,25 @@
         <v>28</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="213">
       <c r="A8" s="12" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="87"/>
+        <v>95</v>
+      </c>
+      <c r="D8" s="92"/>
       <c r="E8" s="5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G8" s="8">
         <v>0</v>
@@ -2543,25 +3156,25 @@
         <v>50</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="106.5">
       <c r="A9" s="12" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="88"/>
+        <v>91</v>
+      </c>
+      <c r="D9" s="93"/>
       <c r="E9" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -2570,12 +3183,12 @@
         <v>1600</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15">
       <c r="A12" s="15" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2611,179 +3224,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="26" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30.75">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="95" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="95" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="45.75">
+      <c r="A6" s="95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30.75">
+      <c r="A7" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30.75">
+      <c r="A8" s="95" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30.75">
+      <c r="A9" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="95" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="96" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="96" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30.75">
+      <c r="A12" s="95" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="96" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="96" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="96" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="96" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="95" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="65" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="92" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="65" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="92" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="65" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="92" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="65" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="45.75">
-      <c r="A6" s="92" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="65" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30.75">
-      <c r="A7" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="65" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30.75">
-      <c r="A8" s="92" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="65" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30.75">
-      <c r="A9" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="65" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="92" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="93" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="92" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="93" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30.75">
-      <c r="A12" s="92" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="65" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="92" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="93" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="92" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="93" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="93" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="92" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="93" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="92" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="65" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="93" t="s">
-        <v>98</v>
+      <c r="B18" s="96" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
-      <c r="A19" s="92" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="93" t="s">
-        <v>100</v>
+      <c r="A19" s="95" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="96" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="92" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="93" t="s">
-        <v>101</v>
+      <c r="A20" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="96" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="94" t="s">
-        <v>102</v>
+      <c r="B21" s="97" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="92" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="93" t="s">
-        <v>104</v>
+      <c r="A22" s="95" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="96" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2792,6 +3405,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2802,9 +3424,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2829,6 +3451,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2908,6 +3531,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3051,23 +3679,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BBB17A7-BDD0-4B44-881E-B1716FC76EE9}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59E2BBB-56D0-4464-BD32-20D477792EEA}"/>
 </file>
--- a/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Kosovo - Energy Projects.xlsx
@@ -395,7 +395,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -683,9 +683,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -802,6 +799,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K21" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L21" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2328,33 +2345,29 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K21" s="101" t="n">
+      <c r="K21" s="102" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="102" t="n"/>
-      <c r="M21" s="103" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N21" s="104" t="n"/>
-      <c r="O21" s="104" t="n"/>
-      <c r="P21" s="105" t="n"/>
-      <c r="Q21" s="106" t="n"/>
-      <c r="R21" s="107" t="n"/>
-      <c r="S21" s="107" t="n"/>
-      <c r="T21" s="107" t="n"/>
-      <c r="U21" s="107" t="n"/>
-      <c r="V21" s="108" t="n"/>
-      <c r="W21" s="107" t="n"/>
-      <c r="X21" s="108" t="n"/>
-      <c r="Y21" s="109" t="n"/>
-      <c r="Z21" s="109" t="n"/>
-      <c r="AA21" s="110" t="n"/>
-      <c r="AB21" s="110" t="n"/>
-      <c r="AC21" s="110" t="n"/>
-      <c r="AD21" s="110" t="n"/>
-      <c r="AE21" s="110" t="n"/>
+      <c r="M21" s="66" t="n"/>
+      <c r="N21" s="103" t="n"/>
+      <c r="O21" s="103" t="n"/>
+      <c r="P21" s="104" t="n"/>
+      <c r="Q21" s="105" t="n"/>
+      <c r="R21" s="106" t="n"/>
+      <c r="S21" s="106" t="n"/>
+      <c r="T21" s="106" t="n"/>
+      <c r="U21" s="106" t="n"/>
+      <c r="V21" s="107" t="n"/>
+      <c r="W21" s="106" t="n"/>
+      <c r="X21" s="107" t="n"/>
+      <c r="Y21" s="108" t="n"/>
+      <c r="Z21" s="108" t="n"/>
+      <c r="AA21" s="109" t="n"/>
+      <c r="AB21" s="109" t="n"/>
+      <c r="AC21" s="109" t="n"/>
+      <c r="AD21" s="109" t="n"/>
+      <c r="AE21" s="109" t="n"/>
     </row>
     <row r="22"/>
     <row r="23"/>
@@ -2362,7 +2375,7 @@
       <c r="A24" s="15" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="Q2:Q20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -2396,12 +2409,6 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -2410,6 +2417,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2544,7 +2552,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D2" s="111" t="n">
+      <c r="D2" s="110" t="n">
         <v>1150000</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2607,7 +2615,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D3" s="112" t="n"/>
+      <c r="D3" s="111" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Transport Services</t>
@@ -2671,7 +2679,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D4" s="112" t="n"/>
+      <c r="D4" s="111" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2730,7 +2738,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D5" s="113" t="n"/>
+      <c r="D5" s="112" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -2779,7 +2787,7 @@
           <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
         </is>
       </c>
-      <c r="D6" s="114" t="n">
+      <c r="D6" s="113" t="n">
         <v>704052</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2825,7 +2833,7 @@
           <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
         </is>
       </c>
-      <c r="D7" s="112" t="n"/>
+      <c r="D7" s="111" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Education Services</t>
@@ -2859,12 +2867,12 @@
           <t>Climate Promise Project- "Growth Through Green and Rapid Recovery from Covid-19"</t>
         </is>
       </c>
-      <c r="C8" s="115" t="inlineStr">
+      <c r="C8" s="114" t="inlineStr">
         <is>
           <t>https://boostimpact.org/challenges/the-kosovo-green-challenge/</t>
         </is>
       </c>
-      <c r="D8" s="112" t="n"/>
+      <c r="D8" s="111" t="n"/>
       <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -2888,10 +2896,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="113" t="n"/>
-      <c r="B9" s="113" t="n"/>
-      <c r="C9" s="113" t="n"/>
-      <c r="D9" s="112" t="n"/>
+      <c r="A9" s="112" t="n"/>
+      <c r="B9" s="112" t="n"/>
+      <c r="C9" s="112" t="n"/>
+      <c r="D9" s="111" t="n"/>
       <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
@@ -2924,7 +2932,7 @@
           <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
         </is>
       </c>
-      <c r="D10" s="113" t="n"/>
+      <c r="D10" s="112" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -3070,7 +3078,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D2" s="116" t="n">
+      <c r="D2" s="115" t="n">
         <v>1150000</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -3117,7 +3125,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D3" s="112" t="n"/>
+      <c r="D3" s="111" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
@@ -3161,7 +3169,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D4" s="112" t="n"/>
+      <c r="D4" s="111" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -3205,7 +3213,7 @@
           <t>https://www.undp.org/kosovo/projects/strengthening-local-climate-action-project#:~:text=The%20project%20supports%20Kosovo%20municipalities,Municipality%20of%20Suharek%C3%AB%2FSuva%20Reka.</t>
         </is>
       </c>
-      <c r="D5" s="113" t="n"/>
+      <c r="D5" s="112" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -3249,7 +3257,7 @@
           <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
         </is>
       </c>
-      <c r="D6" s="117" t="n">
+      <c r="D6" s="116" t="n">
         <v>704052</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -3290,7 +3298,7 @@
           <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
         </is>
       </c>
-      <c r="D7" s="112" t="n"/>
+      <c r="D7" s="111" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Education Services</t>
@@ -3329,7 +3337,7 @@
           <t>https://boostimpact.org/challenges/the-kosovo-green-challenge/</t>
         </is>
       </c>
-      <c r="D8" s="112" t="n"/>
+      <c r="D8" s="111" t="n"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
@@ -3368,7 +3376,7 @@
           <t>https://climatepromise.undp.org/what-we-do/where-we-work/kosovo</t>
         </is>
       </c>
-      <c r="D9" s="113" t="n"/>
+      <c r="D9" s="112" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -3422,288 +3430,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="118" t="inlineStr">
+      <c r="A1" s="117" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="118" t="inlineStr">
+      <c r="B1" s="117" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30.75" customHeight="1">
-      <c r="A2" s="119" t="inlineStr">
+      <c r="A2" s="118" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="119" t="inlineStr">
+      <c r="B2" s="118" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="119" t="inlineStr">
+      <c r="A3" s="118" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="119" t="inlineStr">
+      <c r="B3" s="118" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="119" t="inlineStr">
+      <c r="A4" s="118" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="119" t="inlineStr">
+      <c r="B4" s="118" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="119" t="inlineStr">
+      <c r="A5" s="118" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="119" t="inlineStr">
+      <c r="B5" s="118" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45.75" customHeight="1">
-      <c r="A6" s="119" t="inlineStr">
+      <c r="A6" s="118" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="119" t="inlineStr">
+      <c r="B6" s="118" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="119" t="inlineStr">
+      <c r="A7" s="118" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="119" t="inlineStr">
+      <c r="B7" s="118" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="119" t="inlineStr">
+      <c r="A8" s="118" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="119" t="inlineStr">
+      <c r="B8" s="118" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="119" t="inlineStr">
+      <c r="A9" s="118" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="119" t="inlineStr">
+      <c r="B9" s="118" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="119" t="inlineStr">
+      <c r="A10" s="118" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="119" t="inlineStr">
+      <c r="B10" s="118" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="119" t="inlineStr">
+      <c r="A11" s="118" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="119" t="inlineStr">
+      <c r="B11" s="118" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="119" t="inlineStr">
+      <c r="A12" s="118" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="119" t="inlineStr">
+      <c r="B12" s="118" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="119" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="119" t="inlineStr">
+      <c r="B13" s="118" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="119" t="inlineStr">
+      <c r="A14" s="118" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="119" t="inlineStr">
+      <c r="B14" s="118" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="119" t="inlineStr">
+      <c r="A15" s="118" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="119" t="inlineStr">
+      <c r="B15" s="118" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="119" t="inlineStr">
+      <c r="A16" s="118" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="119" t="inlineStr">
+      <c r="B16" s="118" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="119" t="inlineStr">
+      <c r="A17" s="118" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="119" t="inlineStr">
+      <c r="B17" s="118" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="119" t="inlineStr">
+      <c r="A18" s="118" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="119" t="inlineStr">
+      <c r="B18" s="118" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45.75" customHeight="1">
-      <c r="A19" s="119" t="inlineStr">
+      <c r="A19" s="118" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="119" t="inlineStr">
+      <c r="B19" s="118" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="119" t="inlineStr">
+      <c r="A20" s="118" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="119" t="inlineStr">
+      <c r="B20" s="118" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30.75" customHeight="1">
-      <c r="A21" s="119" t="inlineStr">
+      <c r="A21" s="118" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="119" t="inlineStr">
+      <c r="B21" s="118" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="119" t="inlineStr">
+      <c r="A22" s="118" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="119" t="inlineStr">
+      <c r="B22" s="118" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="119" t="inlineStr">
+      <c r="A23" s="118" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="119" t="inlineStr">
+      <c r="B23" s="118" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="119" t="inlineStr">
+      <c r="A24" s="118" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="119" t="inlineStr">
+      <c r="B24" s="118" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
